--- a/57/food/tm2026-sm.xlsx
+++ b/57/food/tm2026-sm.xlsx
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C1" s="55" t="inlineStr">
         <is>
-          <t>НОУ ГБПОУ "Грозненский педагогический колледж"</t>
+          <t>НОШ ГБПОУ "Грозненский педагогический колледж"</t>
         </is>
       </c>
       <c r="D1" s="58" t="n"/>
